--- a/data/2026/36-teleorman/151790-alexandria/budget_file.xlsx
+++ b/data/2026/36-teleorman/151790-alexandria/budget_file.xlsx
@@ -35,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +52,11 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,13 +70,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1905,41 +1912,39 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>51.02</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>Autoritati publice si actiuni externe</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription); cell re-read from image (unverified transcription)</t>
+      <c r="G43" s="7" t="n"/>
+      <c r="H43" s="7" t="n"/>
+      <c r="I43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column est2027; unparseable cell "00'0" in column est2028</t>
         </is>
       </c>
     </row>
@@ -1983,46 +1988,45 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>51.02</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>Titlul XII ACTIVE NEFINANCIARE</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="G45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="7" t="n"/>
+      <c r="I45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column est2028</t>
         </is>
       </c>
     </row>
@@ -2061,41 +2065,39 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>51.02.01.03</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Autorități executive</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription); cell re-read from image (unverified transcription)</t>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="7" t="n"/>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column est2027; unparseable cell "00'0" in column est2029</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3829,20 +3831,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>48.02</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p2: 5 cells recovered</t>
+          <t>name mismatch vs nomenclator (18%): 'VENITURII PROPRII' vs 'Sume primite de la UE/alti donatori in c'</t>
         </is>
       </c>
     </row>
@@ -3858,16 +3865,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48.02</t>
+          <t>43.02.48.03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'VENITURII PROPRII' vs 'Sume primite de la UE/alti donatori in c'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Sume aferente TVA'</t>
         </is>
       </c>
     </row>
@@ -3887,12 +3894,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.02.48.03</t>
+          <t>43.02.49</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume aferente TVA'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Sume alocate din PNRR aferente asistențe'</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3919,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.02.49</t>
+          <t>43.02.49.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume alocate din PNRR aferente asistențe'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Fonduri europene nerambursabile'</t>
         </is>
       </c>
     </row>
@@ -3937,12 +3944,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.02.49.01</t>
+          <t>43.02.49.03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Fonduri europene nerambursabile'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Sume aferente TVA'</t>
         </is>
       </c>
     </row>
@@ -3962,12 +3969,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.02.49.03</t>
+          <t>45.02.48.01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume aferente TVA'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Sume primite în contul plăţilor efectuat'</t>
         </is>
       </c>
     </row>
@@ -3987,12 +3994,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.02.48.01</t>
+          <t>45.02.48.03</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume primite în contul plăţilor efectuat'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Prefinantare'</t>
         </is>
       </c>
     </row>
@@ -4012,12 +4019,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.02.48.03</t>
+          <t>45.02.49.01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Prefinantare'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Sume primite în contul plăţilor efectuat'</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4044,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.02.49.01</t>
+          <t>45.02.49.02</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4049,77 +4056,67 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>45.02.49.02</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume primite în contul plăţilor efectuat'</t>
+          <t>unparseable cell "00'0" in column est2027</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>51.02</t>
-        </is>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell "00'0" in column est2028</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>51.02</t>
-        </is>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>est2028</t>
@@ -4127,97 +4124,82 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell "00'0" in column est2028</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell "00'0" in column est2027</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>51.02.01.03</t>
-        </is>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2029</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell "00'0" in column est2029</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>51.02.01.03</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>est2029</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -4237,12 +4219,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (38%): 'Din total capitol:' vs 'TITLUL XVII ACTIVE FINANCIARE'</t>
         </is>
       </c>
     </row>
@@ -4262,12 +4244,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70.02.05</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'Din total capitol:' vs 'TITLUL XVII ACTIVE FINANCIARE'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Alimentare cu apa si amenajari hidrotehn'</t>
         </is>
       </c>
     </row>
@@ -4287,12 +4269,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>70.02.05</t>
+          <t>70.02.05.01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Alimentare cu apa si amenajari hidrotehn'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Alimentare cu apa'</t>
         </is>
       </c>
     </row>
@@ -4312,12 +4294,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>70.02.05.01</t>
+          <t>70.02.50</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Alimentare cu apa'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Alte servicii în domeniile locuintelor, '</t>
         </is>
       </c>
     </row>
@@ -4337,12 +4319,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>70.02.50</t>
+          <t>84.02.03.02</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Alte servicii în domeniile locuintelor, '</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Transport în comun'</t>
         </is>
       </c>
     </row>
@@ -4362,35 +4344,10 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>84.02.03.02</t>
+          <t>84.02.03.03</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Transport în comun'</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>84.02.03.03</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (0%): '' vs 'Strazi'</t>
         </is>
@@ -4407,7 +4364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4429,7 +4386,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4439,72 +4396,230 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>87</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>68</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Modele LLM folosite</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash</t>
-        </is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>78.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>80.09999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>78.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>795865ee2396dde8a3911e93</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>09d17a11457e42458692b2375b14e5e6d5a1974f2a7f96ebc443f457bc864d9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>— Anexa (de la pagina 1)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 1-4, 92 linii</t>
         </is>

--- a/data/2026/36-teleorman/151790-alexandria/budget_file.xlsx
+++ b/data/2026/36-teleorman/151790-alexandria/budget_file.xlsx
@@ -35,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -52,11 +52,6 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -70,15 +65,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,12 +446,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -525,7 +527,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>VENITURILE SECTIUNII DE DEZVOLTARE - TOTAL</t>
+          <t>VENITURILE SECŢIUNII DE DEZVOLTARE - TOTAL</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -554,7 +556,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>VENITURII PROPRII</t>
         </is>
@@ -568,13 +570,13 @@
           <t>revenue</t>
         </is>
       </c>
-      <c r="G3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5" t="n">
+      <c r="G3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -684,7 +686,7 @@
           <t>37.02</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Transferuri voluntare, altele decat subventiile</t>
         </is>
@@ -715,7 +717,7 @@
     <row r="8">
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Vărsăminte din secțiunea de funcționare</t>
+          <t>Vărsăminte din secţiunea de funcţionare</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -743,7 +745,7 @@
           <t>39.02</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Venituri din valorificarea unor bunuri</t>
         </is>
@@ -771,13 +773,13 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>39.02.01</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Venituri din valorificarea unor bunuri ale institutiilor publice</t>
         </is>
@@ -805,15 +807,15 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>39.02.03</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Venituri din vanzarea locuintelor construite din fondurile statului</t>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Venituri din vanzarea locuintelor construite din fondurile statului Venituri din vanzarea unor bunuri apartinand domeniului privat al</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -845,9 +847,9 @@
           <t>39.02.07</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Venituri din vanzarea unor bunuri apartinand domeniului privat al statului sau al unitatilor administrativ-teritoriale</t>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>statului sau al unitatilor administrativ-teritoriale</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -879,7 +881,7 @@
           <t>40.02</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Încasări din rambursarea împrumuturilor acordate</t>
         </is>
@@ -907,15 +909,15 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>40.02.14</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Sume din excedentul bugetului local utilizate pentru finanțarea cheltuielilor secțiunii de dezvoltare</t>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Sume din excedentul bugetului local utilizate pentru finanţarea cheltuielilor secţiunii de dezvoltare</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -941,7 +943,7 @@
           <t>42.02</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Subventii de la bugetul de stat</t>
         </is>
@@ -969,13 +971,13 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>42.02.01</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Retehnologizarea centralelor termice si electrice de termoficare</t>
         </is>
@@ -1003,15 +1005,15 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
           <t>42.02.13</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Subvenții pentru finanțarea programelor multianuale prioritare de mediu și gospodărire a apelor</t>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Subvenţii pentru finanţarea programelor multianuale prioritare de mediu şi gospodărire a apelor</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1037,15 +1039,15 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
           <t>42.02.20</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Subvenții de la bugetul de stat catre bugetele locale necesare sustinerii derularii proiectelor finantate din FEN postaderare</t>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Subvenţii de la bugetul de stat catre bugetele locale necesare sustinerii derularii proiectelor finantate din FEN postaderare</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1077,9 +1079,9 @@
           <t>42.02.65</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Finanțarea Programului Național de Dezvoltare Locală</t>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Finanţarea Programului Naţional de Dezvoltare Locală</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1105,15 +1107,15 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
           <t>42.02.69</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Subvenții de la bugetul de stat către bugetele locale necesare susținerii derulării proiectelor finanțate din fonduri externe nerambursabile (FEN) postaderare aferete perioadei de programare 2014-2020</t>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Subvenţii de la bugetul de stat către bugetele locale necesare susţinerii derulării proiectelor finanţate din fonduri externe nerambursabile (FEN) postaderare aferete perioadei de programare 2014-2020</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1139,13 +1141,13 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
           <t>42.02.88</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Alocări de sume din PNRR aferente asistenței financiare nerambursabile</t>
         </is>
@@ -1173,13 +1175,13 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>42.02.79</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Subvenții pentru finanțarea liceelor tehnologice cu profil preponderent agricol</t>
         </is>
@@ -1207,15 +1209,15 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>42.02.87</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Subvenții de la bugetul de stat către bugetele locale pentru Programul național de investiții Anghel Saligny"</t>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Subvenții de la bugetul de stat către bugetele locale pentru Programul național de investiții 'Anghel Saligny'</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1247,7 +1249,7 @@
           <t>42.02.89</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Alocări de sume din PNRR aferente componentei împrumuturi</t>
         </is>
@@ -1275,15 +1277,15 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>42.02.93</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Subvenții de la bugetul de stat necesare susținerii derulării proiectelor finanțate din fonduri externe nerambursabile (FEN) postaderare, aferete perioadei de programare 2021-2027</t>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Subvenţii de la bugetul de stat necesare susţinerii derulării proiectelor finanţate din fonduri externe nerambursabile (FEN) postaderare, aferete perioadei de programare 2021-2027</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1309,15 +1311,15 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>42.02.93.03</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Subvenții de la bugetul de stat către bugetele locale necesare susținerii derulării proiectelor finanțate din FEN postaderare, aferente perioadei de programare 2021-2027</t>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Subvenţii de la bugetul de stat către bugetele locale necesare susţinerii derulării proiectelor finanţate din FEN postaderare, aferente perioadei de programare 2021-2027</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1349,7 +1351,7 @@
           <t>43.02</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Subventii de la alte administratii</t>
         </is>
@@ -1377,13 +1379,13 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
           <t>43.02.44</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Sume alocate din sumele obținute în urma scoaterii la licitație a certificatelor de emisii de gaze cu efect de seră pentru finanțarea proiectelor de investiții</t>
         </is>
@@ -1417,9 +1419,9 @@
           <t>43.02.48</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Sume alocate din PNRR aferente componentei împrumuturi</t>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>împrumuturi</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1451,7 +1453,7 @@
           <t>43.02.48.01</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Fonduri din împrumut rambursabil</t>
         </is>
@@ -1480,150 +1482,138 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>43.02.48.03</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="inlineStr"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n">
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Sume aferente TVA</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
         <v>2</v>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume aferente TVA'</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>43.02.49</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="inlineStr"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n">
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Sume alocate din PNRR aferente asistenței financiare nerambursabile</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume alocate din PNRR aferente asistențe'</t>
+      <c r="G32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>43.02.49.01</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n">
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Fonduri europene nerambursabile</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Fonduri europene nerambursabile'</t>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>43.02.49.03</t>
         </is>
       </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n">
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Sume aferente TVA</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
         <v>2</v>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume aferente TVA'</t>
+      <c r="G34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -1633,9 +1623,9 @@
           <t>45.02</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Sume primite de la UE/alti donatori in contul platilor efectuate si prefinantari</t>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>contul platilor efectuate si prefinantari</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1667,9 +1657,9 @@
           <t>45.02.48</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Fondul European de Dezvoltare Regionala</t>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Regionala</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1696,86 +1686,80 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>45.02.48.01</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="inlineStr"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n">
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Sume primite în contul plăţilor efectuate în anii anteriori</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G37" s="5" t="n">
+      <c r="G37" s="3" t="n">
         <v>29072.07</v>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H37" s="3" t="n">
         <v>29072.07</v>
       </c>
-      <c r="I37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume primite în contul plăţilor efectuat'</t>
+      <c r="I37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>45.02.48.03</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="inlineStr"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n">
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Prefinanţare</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Prefinantare'</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
+      <c r="G38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
           <t>45.02.49</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Fondul Social European Plus (FSE+), aferent cadrului financiar 2021-2027</t>
         </is>
@@ -1804,76 +1788,70 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>45.02.49.01</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="inlineStr"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n">
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Sume primite în contul plăţilor efectuate în anul curent</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume primite în contul plăţilor efectuat'</t>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>45.02.49.02</t>
         </is>
       </c>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="inlineStr"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n">
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Sume primite în contul plăţilor efectuate în anii anteriori</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
         <v>2</v>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume primite în contul plăţilor efectuat'</t>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -1883,19 +1861,15 @@
           <t>49.02</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CHELTUIELILE SECTIUNII DE DEZVOLTARE</t>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>CHELTUIELILE SECŢIUNII DE DEZVOLTARE</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>2</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" s="3" t="n">
         <v>42858.35</v>
       </c>
@@ -1912,43 +1886,40 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>51.02</t>
         </is>
       </c>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Autoritati publice si actiuni externe</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n">
+      <c r="E43" t="n">
         <v>2</v>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G43" s="7" t="n"/>
-      <c r="H43" s="7" t="n"/>
-      <c r="I43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K43" s="6" t="inlineStr">
-        <is>
-          <t>unparseable cell "00'0" in column est2027; unparseable cell "00'0" in column est2028</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
           <t>58</t>
@@ -1959,7 +1930,7 @@
           <t>51.02</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>TITLUL X Proiecte cu finanțare din fonduri externe nerambursabile aferente cadrului financiar 2014-2020</t>
         </is>
@@ -1988,45 +1959,41 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>51.02</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>Titlul XII ACTIVE NEFINANCIARE</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="6" t="n">
+      <c r="E45" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="7" t="n"/>
-      <c r="I45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K45" s="6" t="inlineStr">
-        <is>
-          <t>unparseable cell "00'0" in column est2028</t>
+      <c r="G45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -2036,9 +2003,9 @@
           <t>51.02.01</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Din total capitol: Autoritati executive si legislative</t>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Autoritati executive si legislative</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2049,12 +2016,8 @@
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n">
         <v>0</v>
       </c>
@@ -2065,70 +2028,52 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>51.02.01.03</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Autorități executive</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n">
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Autorităţi executive</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G47" s="7" t="n"/>
-      <c r="H47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="7" t="n"/>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K47" s="6" t="inlineStr">
-        <is>
-          <t>unparseable cell "00'0" in column est2027; unparseable cell "00'0" in column est2029</t>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>54.02</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Alte servicii publice generale</t>
-        </is>
-      </c>
+      <c r="C48" s="2" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I48" s="3" t="n"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -2138,17 +2083,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
           <t>54.02</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Titlul XII ACTIVE NEFINANCIARE Din total capitol:</t>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Alte servicii publice generale</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2156,7 +2096,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>expense_economic</t>
+          <t>expense_functional</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
@@ -2177,12 +2117,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>54.02.10</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Servicii publice comunitare de evidență a persoanelor</t>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>54.02</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Titlul XII ACTIVE NEFINANCIARE Din total capitol:</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -2190,7 +2135,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>expense_functional</t>
+          <t>expense_economic</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
@@ -2211,12 +2156,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ordine publica si siguranta nationala</t>
+          <t>54.02.10</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Servicii publice comunitare de evidenţă a persoanelor</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -2245,17 +2190,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
           <t>61.02</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Titlul XII ACTIVE NEFINANCIARE Din total capitol:</t>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Ordine publica si siguranta nationala</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -2263,7 +2203,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>expense_economic</t>
+          <t>expense_functional</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
@@ -2284,12 +2224,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>61.02.03</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ordine publica</t>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>61.02</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Titlul XII ACTIVE NEFINANCIARE Din total capitol:</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2297,7 +2242,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>expense_functional</t>
+          <t>expense_economic</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
@@ -2318,12 +2263,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>61.02.03.04</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Politie Locala</t>
+          <t>61.02.03</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Ordine publica</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2352,12 +2297,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>61.02.05</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Protectie civila și protecția contra incendiilor (protecție civilă nonmilitară)</t>
+          <t>61.02.03.04</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Politie Locala</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -2383,15 +2328,15 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="30" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Invatamant</t>
+          <t>61.02.05</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Protectie civila şi protecţia contra incendiilor (protecţie civilă nonmilitară)</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2403,10 +2348,10 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>12786.28</v>
+        <v>0</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>12786.28</v>
+        <v>0</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>0</v>
@@ -2420,17 +2365,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
           <t>65.02</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Titlul VII ALTE TRANSFERURI</t>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Invatamant</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -2438,14 +2378,14 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>expense_economic</t>
+          <t>expense_functional</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>12786.28</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>12786.28</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>0</v>
@@ -2459,7 +2399,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2467,9 +2407,9 @@
           <t>65.02</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Titlul VIII Proiecte cu finantare din Fonduri externe nerambursabile (FEN) postaderare</t>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>Titlul VII ALTE TRANSFERURI</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2481,10 +2421,10 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>12786.28</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>12786.28</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>0</v>
@@ -2495,10 +2435,10 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="30" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2506,9 +2446,9 @@
           <t>65.02</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Titlul XIl Proiecte cu finanțare din sumele reprezentând asistența financiară nerambursabilă aferentă PNRR</t>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Titlul VIII Proiecte cu finantare din Fonduri externe nerambursabile (FEN) postaderare</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2520,10 +2460,10 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0</v>
+        <v>12786.28</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0</v>
+        <v>12786.28</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>0</v>
@@ -2534,10 +2474,10 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="30" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2545,9 +2485,9 @@
           <t>65.02</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Titlul XIII Proiecte cu finanțare din sumele aferente componentei de împrumuturi a PNRR</t>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Titlul XII Proiecte cu finanțare din sumele reprezentând asistența financiară nerambursabilă aferentă PNRR</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2558,19 +2498,25 @@
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G60" s="3" t="n"/>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="3" t="n"/>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>ocr</t>
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="30" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2578,9 +2524,9 @@
           <t>65.02</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Titlul XII ACTIVE NEFINANCIARE</t>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Titlul XIII Proiecte cu finanțare din sumele aferente componentei de împrumuturi a PNRR</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2591,15 +2537,9 @@
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+      <c r="I61" s="3" t="n"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -2609,12 +2549,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Sanatate</t>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Titlul XII ACTIVE NEFINANCIARE</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2622,7 +2567,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>expense_functional</t>
+          <t>expense_economic</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
@@ -2643,17 +2588,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
           <t>66.02</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>TITLUL X Proiecte cu finanțare din fonduri externe nerambursabile aferente cadrului financiar 2014-2020 Din total capitol:</t>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Sanatate</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2661,7 +2601,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>expense_economic</t>
+          <t>expense_functional</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
@@ -2679,15 +2619,20 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="45" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>66.02.50</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Alte cheltuieli in domeniul sanatati</t>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>TITLUL X Proiecte cu finanțare din fonduri externe nerambursabile aferente cadrului financiar 2014-2020 Din total capitol:</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2695,7 +2640,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>expense_functional</t>
+          <t>expense_economic</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
@@ -2716,12 +2661,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Cultura, recreere si religie</t>
+          <t>66.02.50</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Alte cheltuieli in domeniul sanatati</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2750,17 +2695,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
           <t>67.02</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Titlul VIII Proiecte cu finantare din Fonduri externe nerambursabile (FEN) postaderare</t>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Cultura, recreere si religie</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2768,7 +2708,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>expense_economic</t>
+          <t>expense_functional</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
@@ -2786,10 +2726,10 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="30" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2797,9 +2737,9 @@
           <t>67.02</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>TitluI XII ACTIVE NEFINANCIARE Din total capitol:</t>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Titlul VIII Proiecte cu finantare din Fonduri externe nerambursabile (FEN) postaderare</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2828,12 +2768,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>67.02.05</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Servicii recreative si sportive</t>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Titlul XII ACTIVE NEFINANCIARE Din total capitol:</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2841,7 +2786,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>expense_functional</t>
+          <t>expense_economic</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
@@ -2862,12 +2807,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>67.02.05.03</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Intretinere gradini publice, parcuri, zone verzi, baze sportive si de agrement</t>
+          <t>67.02.05</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>Servicii recreative si sportive</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2893,15 +2838,15 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="30" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>67.02.50</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Alte servicii în domeniile culturii, recreerii si religiei</t>
+          <t>67.02.05.03</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Intretinere gradini publice, parcuri, zone verzi, baze sportive si de agrement</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2930,12 +2875,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Asigurari si asistenta sociala</t>
+          <t>67.02.50</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>Alte servicii în domeniile culturii, recreerii si religiei</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2964,17 +2909,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
           <t>68.02</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Titlul XII ACTIVE NEFINANCIARE Din total capitol:</t>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>Asigurari si asistenta sociala</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2982,7 +2922,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>expense_economic</t>
+          <t>expense_functional</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
@@ -3003,20 +2943,25 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>68.02.50</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Alte cheltuieli in domeniul asigurarilor si asistentei sociale</t>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Titlul XII ACTIVE NEFINANCIARE Din total capitol:</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>expense_functional</t>
+          <t>expense_economic</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
@@ -3037,12 +2982,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Locuinte, servicii si dezvoltare publica</t>
+          <t>68.02.50</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>cheltuieli in domeniul asigurarilor si asistentei sociale</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -3054,10 +2999,10 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>30072.07</v>
+        <v>0</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>29072.07</v>
+        <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>0</v>
@@ -3071,17 +3016,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
           <t>70.02</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Titlul VII ALTE TRANSFERURI</t>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Locuinte, servicii si dezvoltare publica</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -3089,14 +3029,14 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>expense_economic</t>
+          <t>expense_functional</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1000</v>
+        <v>30072.07</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0</v>
+        <v>29072.07</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0</v>
@@ -3110,7 +3050,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3118,9 +3058,9 @@
           <t>70.02</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Titlul VIII Proiecte cu finantare din Fonduri externe nerambursabile (FEN) postaderare</t>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>Titlul VII ALTE TRANSFERURI</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -3132,10 +3072,10 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>29072.07</v>
+        <v>1000</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>29072.07</v>
+        <v>0</v>
       </c>
       <c r="I76" s="3" t="n">
         <v>0</v>
@@ -3146,10 +3086,10 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="30" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3157,9 +3097,9 @@
           <t>70.02</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Titlul XII Proiecte cu finanțare din sumele reprezentând asistența financiară nerambursabilă aferentă PNRR</t>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Titlul VIII Proiecte cu finantare din Fonduri externe nerambursabile (FEN) postaderare</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -3171,224 +3111,212 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0</v>
+        <v>29072.07</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="3" t="n"/>
+        <v>29072.07</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>ocr</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Titlul XII Proiecte cu finanțare din sumele reprezentând asistența financiară nerambursabilă aferentă PNRR</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>4</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3" t="n"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>70.02</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr"/>
-      <c r="D78" s="4" t="n"/>
-      <c r="E78" s="4" t="n">
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE NEFINANCIARE</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
         <v>4</v>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K78" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="G79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>70.02</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>Din total capitol:</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="n">
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE FINANCIARE Din total capitol:</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
         <v>4</v>
       </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G79" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K79" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (38%): 'Din total capitol:' vs 'TITLUL XVII ACTIVE FINANCIARE'</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="G80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>70.02.05</t>
         </is>
       </c>
-      <c r="B80" s="4" t="n"/>
-      <c r="C80" s="4" t="inlineStr"/>
-      <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="n">
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>cu apa si amenajari hidrotehnice</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
         <v>4</v>
       </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K80" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Alimentare cu apa si amenajari hidrotehn'</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="G81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>70.02.05.01</t>
         </is>
       </c>
-      <c r="B81" s="4" t="n"/>
-      <c r="C81" s="4" t="inlineStr"/>
-      <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n">
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Alimentare cu apa</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
         <v>4</v>
       </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G81" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K81" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Alimentare cu apa'</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="G82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>70.02.50</t>
         </is>
       </c>
-      <c r="B82" s="4" t="n"/>
-      <c r="C82" s="4" t="inlineStr"/>
-      <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>30072.07</v>
-      </c>
-      <c r="H82" s="5" t="n">
-        <v>29072.07</v>
-      </c>
-      <c r="I82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K82" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Alte servicii în domeniile locuintelor, '</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Transporturi</t>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>servicii în domeniile locuintelor, serviciilor si dezvoltarii comunale</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -3400,10 +3328,10 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0</v>
+        <v>30072.07</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0</v>
+        <v>29072.07</v>
       </c>
       <c r="I83" s="3" t="n">
         <v>0</v>
@@ -3417,17 +3345,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
           <t>84.02</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Titlul VIII Proiecte cu finantare din Fonduri externe nerambursabile (FEN) postaderare</t>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>Transporturi</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -3435,7 +3358,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>expense_economic</t>
+          <t>expense_functional</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
@@ -3453,10 +3376,10 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="30" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3464,9 +3387,9 @@
           <t>84.02</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>TITLUL X Proiecte cu finanțare din fonduri externe nerambursabile aferente cadrului financiar 2014-2020</t>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Titlul VIII Proiecte cu finantare din Fonduri externe nerambursabile (FEN) postaderare</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -3492,10 +3415,10 @@
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="30" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3503,9 +3426,9 @@
           <t>84.02</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>TitluI XII ACTIVE NEFINANCIARE</t>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>TITLUL X Proiecte cu finanțare din fonduri externe nerambursabile aferente cadrului financiar 2014-2020</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -3534,7 +3457,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3542,9 +3465,9 @@
           <t>84.02</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Titlul XIII ACTIVE FINANCIARE</t>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Titlul XII ACTIVE NEFINANCIARE</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -3573,12 +3496,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>TitluI XVII PLATI EFECTUATE IN ANII PRECEDENTI SI RECUPERATE IN ANUL CURENT Din total capitol:</t>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE FINANCIARE</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -3586,7 +3514,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>expense_functional</t>
+          <t>expense_economic</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
@@ -3604,117 +3532,107 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="30" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>84.02.03</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Transport rutier</t>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Titlul XVII PLATI EFECTUATE IN ANII PRECEDENTI SI RECUPERATE IN ANUL CURENT Din total capitol:</t>
         </is>
       </c>
       <c r="E89" t="n">
         <v>4</v>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>84.02.03</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Transport rutier</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="G90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>84.02.03.02</t>
         </is>
       </c>
-      <c r="B90" s="4" t="n"/>
-      <c r="C90" s="4" t="inlineStr"/>
-      <c r="D90" s="4" t="n"/>
-      <c r="E90" s="4" t="n">
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Transport în comun</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
         <v>4</v>
       </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G90" s="5" t="n"/>
-      <c r="H90" s="5" t="n"/>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K90" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Transport în comun'</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>84.02.03.03</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="inlineStr"/>
-      <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K91" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Strazi'</t>
+      <c r="G91" s="3" t="n"/>
+      <c r="H91" s="3" t="n"/>
+      <c r="I91" s="3" t="n"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>96.02</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>VII. REZERVE, EXCEDENT / DEFICIT</t>
+          <t>84.02.03.03</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>Strazi</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -3743,12 +3661,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>99.02</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>DEFICIT 1) (cod 00.01-49.02)</t>
+          <t>96.02</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>VII. REZERVE, EXCEDENT / DEFICIT</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -3769,6 +3687,40 @@
         <v>0</v>
       </c>
       <c r="J93" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>99.02</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>DEFICIT 1) (cod 00.01-49.02)</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>4</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr">
         <is>
           <t>ocr</t>
         </is>
@@ -3785,7 +3737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3850,506 +3802,6 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (18%): 'VENITURII PROPRII' vs 'Sume primite de la UE/alti donatori in c'</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>43.02.48.03</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume aferente TVA'</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>43.02.49</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume alocate din PNRR aferente asistențe'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>43.02.49.01</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Fonduri europene nerambursabile'</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>43.02.49.03</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume aferente TVA'</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>45.02.48.01</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume primite în contul plăţilor efectuat'</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>45.02.48.03</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Prefinantare'</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>45.02.49.01</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume primite în contul plăţilor efectuat'</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>45.02.49.02</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume primite în contul plăţilor efectuat'</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>est2027</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>unparseable cell "00'0" in column est2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>est2028</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>unparseable cell "00'0" in column est2028</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>est2028</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>unparseable cell "00'0" in column est2028</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>est2027</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>unparseable cell "00'0" in column est2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>est2029</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>unparseable cell "00'0" in column est2029</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (38%): 'Din total capitol:' vs 'TITLUL XVII ACTIVE FINANCIARE'</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>70.02.05</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Alimentare cu apa si amenajari hidrotehn'</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>70.02.05.01</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Alimentare cu apa'</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>70.02.50</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Alte servicii în domeniile locuintelor, '</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>84.02.03.02</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Transport în comun'</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>84.02.03.03</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Strazi'</t>
         </is>
       </c>
     </row>
@@ -4372,7 +3824,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Fisier</t>
         </is>
@@ -4384,17 +3836,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Metrica de calitate</t>
         </is>
@@ -4406,7 +3858,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Recall masurat</t>
         </is>
@@ -4418,7 +3870,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Documente</t>
         </is>
@@ -4428,67 +3880,67 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>% linii strict verificate</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>78.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Celule numerice</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>246</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Celule numerice strict verificate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>197</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>% celule numerice strict verificate</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>80.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Pagini asteptate</t>
         </is>
@@ -4498,7 +3950,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Pagini selectate</t>
         </is>
@@ -4508,7 +3960,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Pagini procesate</t>
         </is>
@@ -4518,7 +3970,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>PDF complet</t>
         </is>
@@ -4530,47 +3982,47 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Linii fara probleme</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>% curat</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>78.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Erori</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Avertismente</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Informatii</t>
         </is>
@@ -4580,7 +4032,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Schema publicare</t>
         </is>
@@ -4590,19 +4042,19 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Bundle conversie</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>795865ee2396dde8a3911e93</t>
+          <t>47dd91e0e5afefff5cadf3b2</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>SHA-256 PDF sursa</t>
         </is>
@@ -4614,14 +4066,14 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>— Anexa (de la pagina 1)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>local, pag. 1-4, 92 linii</t>
+          <t>local, pag. 1-4, 93 linii</t>
         </is>
       </c>
     </row>
